--- a/artfynd/A 33513-2025 artfynd.xlsx
+++ b/artfynd/A 33513-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3600815</v>
+        <v>3291516</v>
       </c>
       <c r="B2" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221343</v>
+        <v>221063</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>700 m Ö om Rensbodarna, Jmt</t>
+          <t>510 m NV om Grossmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475807.6022977252</v>
+        <v>476208</v>
       </c>
       <c r="R2" t="n">
-        <v>7032755.948361078</v>
+        <v>7032761</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>1989-07-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-07-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Myrkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3600816</v>
+        <v>3600815</v>
       </c>
       <c r="B3" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,14 +808,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>590 m Ö om Rensbodarna, Jmt</t>
+          <t>700 m Ö om Rensbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475707.1497084927</v>
+        <v>475808</v>
       </c>
       <c r="R3" t="n">
-        <v>7032814.928921091</v>
+        <v>7032756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>1989-07-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1989-07-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,6 +876,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3600816</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>590 m Ö om Rensbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>475707</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7032815</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1989-07-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1989-07-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
